--- a/Submitted_VFCs_of_PatchSeeker.xlsx
+++ b/Submitted_VFCs_of_PatchSeeker.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smu/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A73AF6-C9BF-A144-A8C6-76D1892E3142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$F$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$77</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -86,9 +96,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
       </rPr>
       <t>https://github.com/Chocobozzz/PeerTube/commit/76226d85685220db1495025300eca784d0336f7d</t>
     </r>
@@ -99,10 +110,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Aptos, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://github.com/LabRedesCefetRJ/WeGIA/commit/f535e873a8f26fe413d21f22e3eacc8c79b2fa7f</t>
     </r>
@@ -149,9 +160,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
       </rPr>
       <t>https://github.com/apache/inlong/commit/86c893cfd8f7ba9ffce5d20abef6cd360f502fdf</t>
     </r>
@@ -186,10 +198,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Aptos"/>
-        <color rgb="FF1155CC"/>
-        <sz val="12.0"/>
-        <u/>
       </rPr>
       <t>https://github.com/perl-catalyst/Catalyst-Authentication-Credential-HTTP/commit/ad2c03aad95406db4ce35dfb670664ebde004c18</t>
     </r>
@@ -254,9 +266,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
       </rPr>
       <t>https://github.com/zevv/duc/commit/8638c4365ffd9e1966bdef8af6339dbee8c17e66</t>
     </r>
@@ -315,10 +328,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="&quot;Aptos&quot;,sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://github.com/GitoxideLabs/gitoxide/commit/f253f02a6658b3b7612a50d56c71f5ae4da4ca21</t>
     </r>
@@ -401,10 +414,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Aptos, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://github.com/instaclustr/cassandra-lucene-index/commit/44ab4b639c9354a6335f40b1cf6178c745c6e101</t>
     </r>
@@ -590,54 +603,77 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF1155CC"/>
       <name val="Aptos"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF212121"/>
       <name val="Aptos"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Aptos, sans-serif"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF1155CC"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="&quot;Aptos&quot;,sans-serif"/>
     </font>
   </fonts>
   <fills count="3">
@@ -645,7 +681,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -655,66 +691,51 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -904,21 +925,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F77"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="41.25"/>
-    <col customWidth="1" min="5" max="5" width="37.75"/>
+    <col min="1" max="1" width="41.1640625" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -938,7 +962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -956,7 +980,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -964,17 +988,17 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -992,7 +1016,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1010,14 +1034,14 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="b">
+      <c r="C6" s="4" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="b">
@@ -1028,7 +1052,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -1046,7 +1070,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1064,7 +1088,7 @@
       </c>
       <c r="F8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
@@ -1082,7 +1106,7 @@
       </c>
       <c r="F9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="15">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -1095,12 +1119,12 @@
       <c r="D10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -1118,7 +1142,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -1136,7 +1160,7 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
@@ -1154,7 +1178,7 @@
       </c>
       <c r="F13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
@@ -1172,7 +1196,7 @@
       </c>
       <c r="F14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
@@ -1190,7 +1214,7 @@
       </c>
       <c r="F15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
@@ -1208,7 +1232,7 @@
       </c>
       <c r="F16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1226,11 +1250,11 @@
       </c>
       <c r="F17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="15">
       <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="4" t="b">
@@ -1244,7 +1268,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
@@ -1262,7 +1286,7 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="16">
       <c r="A20" s="3" t="s">
         <v>47</v>
       </c>
@@ -1275,12 +1299,12 @@
       <c r="D20" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>49</v>
       </c>
       <c r="F20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>50</v>
       </c>
@@ -1293,12 +1317,12 @@
       <c r="D21" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>52</v>
       </c>
@@ -1316,7 +1340,7 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>54</v>
       </c>
@@ -1334,7 +1358,7 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>57</v>
       </c>
@@ -1352,7 +1376,7 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>60</v>
       </c>
@@ -1370,7 +1394,7 @@
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>63</v>
       </c>
@@ -1388,7 +1412,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>65</v>
       </c>
@@ -1406,17 +1430,17 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" s="11" t="b">
+      <c r="C28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -1424,7 +1448,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>70</v>
       </c>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1460,7 +1484,7 @@
       </c>
       <c r="F30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>74</v>
       </c>
@@ -1478,7 +1502,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>76</v>
       </c>
@@ -1496,14 +1520,14 @@
       </c>
       <c r="F32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="6" t="b">
+      <c r="C33" s="4" t="b">
         <v>0</v>
       </c>
       <c r="D33" s="4" t="b">
@@ -1514,7 +1538,7 @@
       </c>
       <c r="F33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>80</v>
       </c>
@@ -1532,7 +1556,7 @@
       </c>
       <c r="F34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
@@ -1550,7 +1574,7 @@
       </c>
       <c r="F35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>84</v>
       </c>
@@ -1568,7 +1592,7 @@
       </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="15">
       <c r="A37" s="3" t="s">
         <v>86</v>
       </c>
@@ -1581,12 +1605,12 @@
       <c r="D37" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="6" t="s">
         <v>87</v>
       </c>
       <c r="F37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>88</v>
       </c>
@@ -1604,7 +1628,7 @@
       </c>
       <c r="F38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>90</v>
       </c>
@@ -1622,7 +1646,7 @@
       </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>92</v>
       </c>
@@ -1640,7 +1664,7 @@
       </c>
       <c r="F40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>94</v>
       </c>
@@ -1658,7 +1682,7 @@
       </c>
       <c r="F41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>96</v>
       </c>
@@ -1676,14 +1700,14 @@
       </c>
       <c r="F42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A43" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="6" t="b">
+      <c r="C43" s="4" t="b">
         <v>0</v>
       </c>
       <c r="D43" s="4" t="b">
@@ -1694,7 +1718,7 @@
       </c>
       <c r="F43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>101</v>
       </c>
@@ -1712,14 +1736,14 @@
       </c>
       <c r="F44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="6" t="b">
+      <c r="C45" s="4" t="b">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="b">
@@ -1730,7 +1754,7 @@
       </c>
       <c r="F45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>105</v>
       </c>
@@ -1748,7 +1772,7 @@
       </c>
       <c r="F46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>107</v>
       </c>
@@ -1766,7 +1790,7 @@
       </c>
       <c r="F47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>109</v>
       </c>
@@ -1784,7 +1808,7 @@
       </c>
       <c r="F48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" ht="15">
       <c r="A49" s="3" t="s">
         <v>111</v>
       </c>
@@ -1797,12 +1821,12 @@
       <c r="D49" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="6" t="s">
         <v>113</v>
       </c>
       <c r="F49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" ht="13">
       <c r="A50" s="3" t="s">
         <v>114</v>
       </c>
@@ -1820,7 +1844,7 @@
       </c>
       <c r="F50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="13">
       <c r="A51" s="5" t="s">
         <v>116</v>
       </c>
@@ -1828,17 +1852,17 @@
         <v>6</v>
       </c>
       <c r="C51" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>117</v>
       </c>
       <c r="F51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" ht="13">
       <c r="A52" s="3" t="s">
         <v>118</v>
       </c>
@@ -1856,7 +1880,7 @@
       </c>
       <c r="F52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" ht="13">
       <c r="A53" s="3" t="s">
         <v>120</v>
       </c>
@@ -1874,7 +1898,7 @@
       </c>
       <c r="F53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" ht="13">
       <c r="A54" s="3" t="s">
         <v>122</v>
       </c>
@@ -1892,7 +1916,7 @@
       </c>
       <c r="F54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" ht="13" hidden="1">
       <c r="A55" s="3" t="s">
         <v>124</v>
       </c>
@@ -1910,7 +1934,7 @@
       </c>
       <c r="F55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6" ht="13" hidden="1">
       <c r="A56" s="3" t="s">
         <v>126</v>
       </c>
@@ -1928,7 +1952,7 @@
       </c>
       <c r="F56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" ht="13">
       <c r="A57" s="3" t="s">
         <v>128</v>
       </c>
@@ -1946,7 +1970,7 @@
       </c>
       <c r="F57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" ht="13">
       <c r="A58" s="3" t="s">
         <v>130</v>
       </c>
@@ -1964,7 +1988,7 @@
       </c>
       <c r="F58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" ht="13">
       <c r="A59" s="3" t="s">
         <v>132</v>
       </c>
@@ -1982,7 +2006,7 @@
       </c>
       <c r="F59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" ht="13">
       <c r="A60" s="3" t="s">
         <v>134</v>
       </c>
@@ -2000,7 +2024,7 @@
       </c>
       <c r="F60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" ht="13" hidden="1">
       <c r="A61" s="3" t="s">
         <v>136</v>
       </c>
@@ -2008,17 +2032,17 @@
         <v>6</v>
       </c>
       <c r="C61" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>104</v>
       </c>
       <c r="F61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" ht="13">
       <c r="A62" s="3" t="s">
         <v>137</v>
       </c>
@@ -2036,7 +2060,7 @@
       </c>
       <c r="F62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" ht="13">
       <c r="A63" s="3" t="s">
         <v>140</v>
       </c>
@@ -2044,17 +2068,17 @@
         <v>6</v>
       </c>
       <c r="C63" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>141</v>
       </c>
       <c r="F63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" ht="13" hidden="1">
       <c r="A64" s="3" t="s">
         <v>142</v>
       </c>
@@ -2072,7 +2096,7 @@
       </c>
       <c r="F64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" ht="13">
       <c r="A65" s="3" t="s">
         <v>144</v>
       </c>
@@ -2080,17 +2104,17 @@
         <v>6</v>
       </c>
       <c r="C65" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>145</v>
       </c>
       <c r="F65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" ht="13">
       <c r="A66" s="3" t="s">
         <v>146</v>
       </c>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="F66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6" ht="13" hidden="1">
       <c r="A67" s="3" t="s">
         <v>148</v>
       </c>
@@ -2125,17 +2149,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" ht="13">
       <c r="A68" s="5" t="s">
         <v>150</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C68" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="D68" s="11" t="b">
+      <c r="C68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -2145,7 +2169,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" ht="13">
       <c r="A69" s="3" t="s">
         <v>154</v>
       </c>
@@ -2153,17 +2177,17 @@
         <v>6</v>
       </c>
       <c r="C69" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>155</v>
       </c>
       <c r="F69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" ht="13">
       <c r="A70" s="3" t="s">
         <v>156</v>
       </c>
@@ -2181,7 +2205,7 @@
       </c>
       <c r="F70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6" ht="13">
       <c r="A71" s="3" t="s">
         <v>158</v>
       </c>
@@ -2191,7 +2215,7 @@
       <c r="C71" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="D71" s="11" t="b">
+      <c r="D71" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E71" s="3" t="s">
@@ -2199,7 +2223,7 @@
       </c>
       <c r="F71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6" ht="13" hidden="1">
       <c r="A72" s="3" t="s">
         <v>160</v>
       </c>
@@ -2217,14 +2241,14 @@
       </c>
       <c r="F72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6" ht="13" hidden="1">
       <c r="A73" s="3" t="s">
         <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C73" s="11" t="b">
+      <c r="C73" s="4" t="b">
         <v>0</v>
       </c>
       <c r="D73" s="4" t="b">
@@ -2235,7 +2259,7 @@
       </c>
       <c r="F73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:6" ht="13">
       <c r="A74" s="3" t="s">
         <v>165</v>
       </c>
@@ -2253,7 +2277,7 @@
       </c>
       <c r="F74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" ht="13">
       <c r="A75" s="3" t="s">
         <v>167</v>
       </c>
@@ -2271,7 +2295,7 @@
       </c>
       <c r="F75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" ht="13">
       <c r="A76" s="3" t="s">
         <v>169</v>
       </c>
@@ -2289,7 +2313,7 @@
       </c>
       <c r="F76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" ht="13" hidden="1">
       <c r="A77" s="3" t="s">
         <v>171</v>
       </c>
@@ -2308,164 +2332,171 @@
       <c r="F77" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$F$77"/>
+  <autoFilter ref="A1:F77" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A2"/>
-    <hyperlink r:id="rId2" ref="E2"/>
-    <hyperlink r:id="rId3" ref="A3"/>
-    <hyperlink r:id="rId4" ref="E3"/>
-    <hyperlink r:id="rId5" ref="A4"/>
-    <hyperlink r:id="rId6" ref="E4"/>
-    <hyperlink r:id="rId7" ref="A5"/>
-    <hyperlink r:id="rId8" ref="E5"/>
-    <hyperlink r:id="rId9" ref="A6"/>
-    <hyperlink r:id="rId10" ref="E6"/>
-    <hyperlink r:id="rId11" ref="A7"/>
-    <hyperlink r:id="rId12" ref="E7"/>
-    <hyperlink r:id="rId13" ref="A8"/>
-    <hyperlink r:id="rId14" ref="E8"/>
-    <hyperlink r:id="rId15" ref="A9"/>
-    <hyperlink r:id="rId16" ref="E9"/>
-    <hyperlink r:id="rId17" ref="A10"/>
-    <hyperlink r:id="rId18" ref="E10"/>
-    <hyperlink r:id="rId19" ref="A11"/>
-    <hyperlink r:id="rId20" location="diff-48d27698cc708c7efe770fd897e4885efaa0a15cae30d54936068603ba03bbd9" ref="E11"/>
-    <hyperlink r:id="rId21" ref="A12"/>
-    <hyperlink r:id="rId22" ref="E12"/>
-    <hyperlink r:id="rId23" ref="A13"/>
-    <hyperlink r:id="rId24" ref="E13"/>
-    <hyperlink r:id="rId25" ref="A14"/>
-    <hyperlink r:id="rId26" ref="E14"/>
-    <hyperlink r:id="rId27" ref="A15"/>
-    <hyperlink r:id="rId28" ref="E15"/>
-    <hyperlink r:id="rId29" ref="A16"/>
-    <hyperlink r:id="rId30" ref="E16"/>
-    <hyperlink r:id="rId31" ref="A17"/>
-    <hyperlink r:id="rId32" ref="E17"/>
-    <hyperlink r:id="rId33" ref="A18"/>
-    <hyperlink r:id="rId34" ref="E18"/>
-    <hyperlink r:id="rId35" ref="A19"/>
-    <hyperlink r:id="rId36" ref="E19"/>
-    <hyperlink r:id="rId37" ref="A20"/>
-    <hyperlink r:id="rId38" ref="E20"/>
-    <hyperlink r:id="rId39" ref="A21"/>
-    <hyperlink r:id="rId40" ref="E21"/>
-    <hyperlink r:id="rId41" location="match-20465516" ref="A22"/>
-    <hyperlink r:id="rId42" ref="E22"/>
-    <hyperlink r:id="rId43" ref="A23"/>
-    <hyperlink r:id="rId44" ref="E23"/>
-    <hyperlink r:id="rId45" ref="A24"/>
-    <hyperlink r:id="rId46" ref="E24"/>
-    <hyperlink r:id="rId47" ref="A25"/>
-    <hyperlink r:id="rId48" ref="E25"/>
-    <hyperlink r:id="rId49" ref="A26"/>
-    <hyperlink r:id="rId50" ref="E26"/>
-    <hyperlink r:id="rId51" ref="A27"/>
-    <hyperlink r:id="rId52" ref="B27"/>
-    <hyperlink r:id="rId53" ref="E27"/>
-    <hyperlink r:id="rId54" ref="A28"/>
-    <hyperlink r:id="rId55" ref="E28"/>
-    <hyperlink r:id="rId56" ref="A29"/>
-    <hyperlink r:id="rId57" ref="E29"/>
-    <hyperlink r:id="rId58" ref="A30"/>
-    <hyperlink r:id="rId59" ref="E30"/>
-    <hyperlink r:id="rId60" ref="A31"/>
-    <hyperlink r:id="rId61" ref="E31"/>
-    <hyperlink r:id="rId62" ref="A32"/>
-    <hyperlink r:id="rId63" ref="E32"/>
-    <hyperlink r:id="rId64" ref="A33"/>
-    <hyperlink r:id="rId65" ref="E33"/>
-    <hyperlink r:id="rId66" ref="A34"/>
-    <hyperlink r:id="rId67" ref="E34"/>
-    <hyperlink r:id="rId68" ref="A35"/>
-    <hyperlink r:id="rId69" ref="E35"/>
-    <hyperlink r:id="rId70" ref="A36"/>
-    <hyperlink r:id="rId71" ref="E36"/>
-    <hyperlink r:id="rId72" ref="A37"/>
-    <hyperlink r:id="rId73" ref="E37"/>
-    <hyperlink r:id="rId74" ref="A38"/>
-    <hyperlink r:id="rId75" ref="E38"/>
-    <hyperlink r:id="rId76" ref="A39"/>
-    <hyperlink r:id="rId77" ref="E39"/>
-    <hyperlink r:id="rId78" ref="A40"/>
-    <hyperlink r:id="rId79" ref="E40"/>
-    <hyperlink r:id="rId80" ref="A41"/>
-    <hyperlink r:id="rId81" ref="B41"/>
-    <hyperlink r:id="rId82" ref="E41"/>
-    <hyperlink r:id="rId83" ref="A42"/>
-    <hyperlink r:id="rId84" ref="E42"/>
-    <hyperlink r:id="rId85" ref="A43"/>
-    <hyperlink r:id="rId86" ref="E43"/>
-    <hyperlink r:id="rId87" ref="A44"/>
-    <hyperlink r:id="rId88" ref="E44"/>
-    <hyperlink r:id="rId89" ref="A45"/>
-    <hyperlink r:id="rId90" ref="E45"/>
-    <hyperlink r:id="rId91" ref="A46"/>
-    <hyperlink r:id="rId92" ref="E46"/>
-    <hyperlink r:id="rId93" ref="A47"/>
-    <hyperlink r:id="rId94" ref="E47"/>
-    <hyperlink r:id="rId95" ref="A48"/>
-    <hyperlink r:id="rId96" ref="E48"/>
-    <hyperlink r:id="rId97" ref="A49"/>
-    <hyperlink r:id="rId98" ref="E49"/>
-    <hyperlink r:id="rId99" ref="A50"/>
-    <hyperlink r:id="rId100" ref="E50"/>
-    <hyperlink r:id="rId101" ref="A51"/>
-    <hyperlink r:id="rId102" ref="E51"/>
-    <hyperlink r:id="rId103" ref="A52"/>
-    <hyperlink r:id="rId104" ref="E52"/>
-    <hyperlink r:id="rId105" ref="A53"/>
-    <hyperlink r:id="rId106" ref="E53"/>
-    <hyperlink r:id="rId107" ref="A54"/>
-    <hyperlink r:id="rId108" ref="E54"/>
-    <hyperlink r:id="rId109" ref="A55"/>
-    <hyperlink r:id="rId110" ref="E55"/>
-    <hyperlink r:id="rId111" ref="A56"/>
-    <hyperlink r:id="rId112" ref="E56"/>
-    <hyperlink r:id="rId113" ref="A57"/>
-    <hyperlink r:id="rId114" ref="E57"/>
-    <hyperlink r:id="rId115" ref="A58"/>
-    <hyperlink r:id="rId116" ref="E58"/>
-    <hyperlink r:id="rId117" ref="A59"/>
-    <hyperlink r:id="rId118" ref="E59"/>
-    <hyperlink r:id="rId119" ref="A60"/>
-    <hyperlink r:id="rId120" ref="E60"/>
-    <hyperlink r:id="rId121" ref="A61"/>
-    <hyperlink r:id="rId122" ref="E61"/>
-    <hyperlink r:id="rId123" ref="A62"/>
-    <hyperlink r:id="rId124" ref="E62"/>
-    <hyperlink r:id="rId125" ref="A63"/>
-    <hyperlink r:id="rId126" ref="E63"/>
-    <hyperlink r:id="rId127" ref="A64"/>
-    <hyperlink r:id="rId128" ref="E64"/>
-    <hyperlink r:id="rId129" ref="A65"/>
-    <hyperlink r:id="rId130" ref="E65"/>
-    <hyperlink r:id="rId131" ref="A66"/>
-    <hyperlink r:id="rId132" ref="E66"/>
-    <hyperlink r:id="rId133" ref="A67"/>
-    <hyperlink r:id="rId134" ref="E67"/>
-    <hyperlink r:id="rId135" ref="A68"/>
-    <hyperlink r:id="rId136" ref="E68"/>
-    <hyperlink r:id="rId137" ref="F68"/>
-    <hyperlink r:id="rId138" ref="A69"/>
-    <hyperlink r:id="rId139" ref="E69"/>
-    <hyperlink r:id="rId140" ref="A70"/>
-    <hyperlink r:id="rId141" ref="E70"/>
-    <hyperlink r:id="rId142" ref="A71"/>
-    <hyperlink r:id="rId143" ref="E71"/>
-    <hyperlink r:id="rId144" ref="A72"/>
-    <hyperlink r:id="rId145" ref="E72"/>
-    <hyperlink r:id="rId146" ref="A73"/>
-    <hyperlink r:id="rId147" ref="E73"/>
-    <hyperlink r:id="rId148" ref="A74"/>
-    <hyperlink r:id="rId149" ref="E74"/>
-    <hyperlink r:id="rId150" ref="A75"/>
-    <hyperlink r:id="rId151" ref="E75"/>
-    <hyperlink r:id="rId152" ref="A76"/>
-    <hyperlink r:id="rId153" ref="E76"/>
-    <hyperlink r:id="rId154" ref="A77"/>
-    <hyperlink r:id="rId155" ref="E77"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E8" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A11" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E11" r:id="rId20" location="diff-48d27698cc708c7efe770fd897e4885efaa0a15cae30d54936068603ba03bbd9" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A13" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="A14" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="E14" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A15" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="E15" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="A16" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="E16" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="A17" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="A18" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E18" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="A19" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="E19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="A20" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="E20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="A21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="E21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="A22" r:id="rId41" location="match-20465516" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E22" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="A23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="E23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="A24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="E24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="A25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="E25" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="A26" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="E26" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="A27" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B27" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="E27" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="A28" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="E28" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="A29" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="E29" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="A30" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="E30" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="A31" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="E31" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="A32" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="E32" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="A33" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="E33" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="A34" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="E34" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="A35" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="E35" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="A36" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="E36" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="A37" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="E37" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="A38" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="E38" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="A39" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="E39" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="A40" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="E40" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="A41" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="B41" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="E41" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="A42" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="E42" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="A43" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="E43" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="A44" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="E44" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="A45" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="E45" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="A46" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="E46" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="A47" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="E47" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="A48" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="E48" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="A49" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="E49" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="A50" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="E50" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="A51" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="E51" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="A52" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="E52" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="A53" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="E53" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="A54" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="E54" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="A55" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="E55" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="A56" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="E56" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="A57" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="E57" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="A58" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="E58" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="A59" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="E59" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="A60" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="E60" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="A61" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="E61" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="A62" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="E62" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="A63" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="E63" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="A64" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="E64" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="A65" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="E65" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="A66" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="E66" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="A67" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="E67" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="A68" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="E68" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F68" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="A69" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="E69" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="A70" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="E70" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="A71" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="E71" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="A72" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="E72" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="A73" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="E73" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="A74" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="E74" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="A75" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="E75" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="A76" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="E76" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="A77" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="E77" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
   </hyperlinks>
-  <drawing r:id="rId156"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>